--- a/reports/一级子公司B_现金流量表_2025-11.xlsx
+++ b/reports/一级子公司B_现金流量表_2025-11.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>45396000</v>
+        <v>45446748</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>520884000</v>
+        <v>520512048</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>981008</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11293379</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>493677</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5639775</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>244749</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2822536</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>197699</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2256780</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>146828</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1692771</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>98763</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1128903</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>73547</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>846030</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>49256</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>564643</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>122952</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1409737</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>61688</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>709483</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>39210</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>448253</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>145500</v>
+        <v>144895</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1669500</v>
+        <v>1670342</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>873000</v>
+        <v>877213</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>10017000</v>
+        <v>10013825</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>46414500</v>
+        <v>48978233</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>23280000</v>
+        <v>23255542</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>267120000</v>
+        <v>266944719</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>327675</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3764618</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>246416</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2819498</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>163364</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1882103</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>123492</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1410095</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>81560</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>940717</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>62094</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>708967</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>8245000</v>
+        <v>8208644</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>94605000</v>
+        <v>94585276</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3104000</v>
+        <v>3114636</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>35616000</v>
+        <v>35630803</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1746000</v>
+        <v>1742358</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>20034000</v>
+        <v>20022394</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>36375000</v>
+        <v>37325781</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>10039500</v>
+        <v>11652452</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>60000</v>
+        <v>59711</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>660000</v>
+        <v>659967</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>600000</v>
+        <v>598187</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6600000</v>
+        <v>6596787</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>360000</v>
+        <v>360573</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3960000</v>
+        <v>3962532</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>660000</v>
+        <v>657898</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>6000000</v>
+        <v>5990408</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>66000000</v>
+        <v>66048448</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>900000</v>
+        <v>902724</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>9900000</v>
+        <v>9893396</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>4200000</v>
+        <v>4182618</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>46200000</v>
+        <v>46224492</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>140000</v>
+        <v>139466</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1540000</v>
+        <v>1539454</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>6140000</v>
+        <v>6129874</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-5480000</v>
+        <v>-5471976</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1200000</v>
+        <v>1202510</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>13200000</v>
+        <v>13190492</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2000000</v>
+        <v>2008825</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>22000000</v>
+        <v>21989604</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2000000</v>
+        <v>1990136</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>22000000</v>
+        <v>22005858</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>60000</v>
+        <v>60296</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>660000</v>
+        <v>659979</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>3260000</v>
+        <v>3271631</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>1600000</v>
+        <v>1605519</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>17600000</v>
+        <v>17607414</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>1600000</v>
+        <v>1596618</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>17600000</v>
+        <v>17589561</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>280000</v>
+        <v>280156</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3080000</v>
+        <v>3082164</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>240000</v>
+        <v>239385</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2640000</v>
+        <v>2641843</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>35000</v>
+        <v>35133</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>385000</v>
+        <v>384777</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>1915000</v>
+        <v>1920808</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1345000</v>
+        <v>1350823</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>5904500</v>
+        <v>7531299</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>5904500</v>
+        <v>7531299</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
